--- a/Result/profitability/3209.xlsx
+++ b/Result/profitability/3209.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.52</v>
       </c>
       <c r="M2" t="n">
-        <v>0.84375</v>
+        <v>0.93125</v>
       </c>
       <c r="N2" t="n">
-        <v>5.41875</v>
+        <v>5.39375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.64</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7925</v>
+        <v>0.93125</v>
       </c>
       <c r="N3" t="n">
-        <v>5.67875</v>
+        <v>5.85625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.85</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8187500000000001</v>
+        <v>0.91875</v>
       </c>
       <c r="N4" t="n">
-        <v>6.296250000000001</v>
+        <v>6.395</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.36</v>
       </c>
       <c r="M5" t="n">
-        <v>0.745</v>
+        <v>1.04375</v>
       </c>
       <c r="N5" t="n">
-        <v>6.631250000000001</v>
+        <v>6.438750000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8875</v>
+        <v>0.9475</v>
       </c>
       <c r="N6" t="n">
-        <v>6.7275</v>
+        <v>6.662500000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7987500000000001</v>
+        <v>0.8375</v>
       </c>
       <c r="N7" t="n">
-        <v>6.867500000000001</v>
+        <v>6.94</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.63</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6975</v>
+        <v>0.7262500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>7.191250000000001</v>
+        <v>7.2125</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0.5687500000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>7.470000000000001</v>
+        <v>7.47</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>0.61</v>
       </c>
       <c r="N10" t="n">
-        <v>7.368749999999999</v>
+        <v>7.36875</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>0.67625</v>
       </c>
       <c r="N11" t="n">
-        <v>7.2625</v>
+        <v>7.262499999999999</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.7162500000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>6.59875</v>
+        <v>6.598749999999999</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>17264</v>
+      </c>
+      <c r="D75" t="n">
+        <v>16366</v>
+      </c>
+      <c r="E75" t="n">
+        <v>898</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>527</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.05%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>29</v>
+      </c>
+      <c r="J75" t="n">
+        <v>556</v>
+      </c>
+      <c r="K75" t="n">
+        <v>413</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.9974999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.1125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1513157894736843</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.03379721669980107</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.734375</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.228486646884273</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
